--- a/V12.6_量化选股结果_20261012.xlsx
+++ b/V12.6_量化选股结果_20261012.xlsx
@@ -573,45 +573,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>software - infrastructure</t>
+          <t>credit services</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8.98</v>
+        <v>20.74</v>
       </c>
       <c r="F2" t="n">
-        <v>0.34</v>
+        <v>0.612</v>
       </c>
       <c r="G2" t="n">
-        <v>19.83</v>
+        <v>22.13</v>
       </c>
       <c r="H2" t="n">
-        <v>2.51</v>
+        <v>5.04</v>
       </c>
       <c r="I2" t="n">
-        <v>22.72</v>
+        <v>10.28</v>
       </c>
       <c r="J2" t="n">
-        <v>0.12</v>
+        <v>0.91</v>
       </c>
       <c r="K2" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N2" t="n">
         <v>5</v>
@@ -620,7 +620,7 @@
         <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>17.7</v>
+        <v>14.4</v>
       </c>
       <c r="Q2" t="n">
         <v>50</v>
@@ -632,19 +632,19 @@
         <v>1.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="U2" t="n">
         <v>0.95</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.406</v>
+        <v>0.579</v>
       </c>
       <c r="Y2" t="n">
         <v>0.8</v>
@@ -668,45 +668,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>JP Morgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>credit services</t>
+          <t>banks - diversified</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20.43</v>
+        <v>2.51</v>
       </c>
       <c r="F3" t="n">
-        <v>0.612</v>
+        <v>0.178</v>
       </c>
       <c r="G3" t="n">
-        <v>22.13</v>
+        <v>25.71</v>
       </c>
       <c r="H3" t="n">
-        <v>5.04</v>
+        <v>1.71</v>
       </c>
       <c r="I3" t="n">
-        <v>10.28</v>
+        <v>14.83</v>
       </c>
       <c r="J3" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.77</v>
+        <v>99</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>70</v>
+        <v>1.98</v>
       </c>
       <c r="N3" t="n">
         <v>5</v>
@@ -715,7 +715,7 @@
         <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>14.4</v>
+        <v>30.4</v>
       </c>
       <c r="Q3" t="n">
         <v>50</v>
@@ -727,19 +727,19 @@
         <v>1.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="U3" t="n">
         <v>0.95</v>
       </c>
       <c r="V3" t="n">
-        <v>0.91</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.571</v>
+        <v>0.393</v>
       </c>
       <c r="Y3" t="n">
         <v>0.8</v>
@@ -763,45 +763,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>consumer electronics</t>
+          <t>internet content &amp; information</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>45.74</v>
+        <v>6.91</v>
       </c>
       <c r="F4" t="n">
-        <v>1.488</v>
+        <v>0.487</v>
       </c>
       <c r="G4" t="n">
-        <v>12.04</v>
+        <v>4.26</v>
       </c>
       <c r="H4" t="n">
-        <v>20.41</v>
+        <v>3.97</v>
       </c>
       <c r="I4" t="n">
-        <v>3.92</v>
+        <v>30.14</v>
       </c>
       <c r="J4" t="n">
-        <v>0.84</v>
+        <v>0.09</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="N4" t="n">
         <v>5</v>
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>16.4</v>
+        <v>24.2</v>
       </c>
       <c r="Q4" t="n">
         <v>50</v>
@@ -822,22 +822,22 @@
         <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="V4" t="n">
-        <v>0.84</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.271</v>
+        <v>0.166</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -858,45 +858,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>internet content &amp; information</t>
+          <t>consumer electronics</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6.91</v>
+        <v>46.1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.487</v>
+        <v>1.488</v>
       </c>
       <c r="G5" t="n">
-        <v>4.26</v>
+        <v>12.04</v>
       </c>
       <c r="H5" t="n">
-        <v>3.97</v>
+        <v>20.41</v>
       </c>
       <c r="I5" t="n">
-        <v>30.14</v>
+        <v>3.92</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09</v>
+        <v>0.84</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="N5" t="n">
         <v>5</v>
@@ -905,7 +905,7 @@
         <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>24.2</v>
+        <v>16.4</v>
       </c>
       <c r="Q5" t="n">
         <v>50</v>
@@ -917,22 +917,22 @@
         <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="U5" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.166</v>
+        <v>0.273</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -953,45 +953,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JP Morgan Chase &amp; Co.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>banks - diversified</t>
+          <t>software - infrastructure</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.5</v>
+        <v>9.07</v>
       </c>
       <c r="F6" t="n">
-        <v>0.178</v>
+        <v>0.34</v>
       </c>
       <c r="G6" t="n">
-        <v>25.71</v>
+        <v>19.83</v>
       </c>
       <c r="H6" t="n">
-        <v>1.71</v>
+        <v>2.51</v>
       </c>
       <c r="I6" t="n">
-        <v>14.83</v>
+        <v>22.72</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="K6" t="n">
-        <v>99</v>
+        <v>0.66</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.98</v>
+        <v>73</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
@@ -1000,7 +1000,7 @@
         <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>30.4</v>
+        <v>17.7</v>
       </c>
       <c r="Q6" t="n">
         <v>50</v>
@@ -1012,7 +1012,7 @@
         <v>1.1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>0.95</v>
@@ -1024,7 +1024,7 @@
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.392</v>
+        <v>0.41</v>
       </c>
       <c r="Y6" t="n">
         <v>0.8</v>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="F7" t="n">
         <v>0.126</v>
@@ -1119,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.307</v>
+        <v>1.331</v>
       </c>
       <c r="Y7" t="n">
         <v>0.8</v>
@@ -1143,45 +1143,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Company (The)</t>
+          <t>AT&amp;T Inc.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>household &amp; personal products</t>
+          <t>telecom services</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.59</v>
+        <v>1.39</v>
       </c>
       <c r="F8" t="n">
-        <v>0.303</v>
+        <v>0.183</v>
       </c>
       <c r="G8" t="n">
-        <v>64.33</v>
+        <v>36.63</v>
       </c>
       <c r="H8" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.07</v>
-      </c>
+        <v>12.37</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>0.84</v>
+        <v>0.47</v>
       </c>
       <c r="K8" t="n">
-        <v>1.42</v>
+        <v>3.69</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
         <v>5</v>
@@ -1190,7 +1188,7 @@
         <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
         <v>50</v>
@@ -1199,22 +1197,22 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.95</v>
+        <v>1.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="V8" t="n">
-        <v>0.84</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.516</v>
+        <v>0.283</v>
       </c>
       <c r="Y8" t="n">
         <v>0.8</v>
@@ -1233,50 +1231,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>美股</t>
+          <t>港股</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>TENCENT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>banks - diversified</t>
+          <t>internet content &amp; information</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.38</v>
+        <v>2.88</v>
       </c>
       <c r="F9" t="n">
-        <v>0.112</v>
+        <v>0.199</v>
       </c>
       <c r="G9" t="n">
-        <v>25.87</v>
+        <v>18.75</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5600000000000001</v>
+        <v>4.85</v>
       </c>
       <c r="I9" t="n">
-        <v>3.49</v>
+        <v>6.1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>99</v>
+        <v>1.59</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.36</v>
+        <v>1.25</v>
       </c>
       <c r="N9" t="n">
         <v>5</v>
@@ -1285,7 +1283,7 @@
         <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>16.8</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
         <v>50</v>
@@ -1297,10 +1295,10 @@
         <v>1.1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.95</v>
+        <v>1.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="V9" t="n">
         <v>0.5</v>
@@ -1309,7 +1307,7 @@
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.575</v>
+        <v>0.431</v>
       </c>
       <c r="Y9" t="n">
         <v>0.8</v>
@@ -1333,43 +1331,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc.</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>telecom services</t>
+          <t>banks - diversified</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>1.38</v>
       </c>
       <c r="F10" t="n">
-        <v>0.183</v>
+        <v>0.112</v>
       </c>
       <c r="G10" t="n">
-        <v>36.63</v>
+        <v>25.87</v>
       </c>
       <c r="H10" t="n">
-        <v>12.37</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.49</v>
+      </c>
       <c r="J10" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.69</v>
+        <v>99</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>2.36</v>
       </c>
       <c r="N10" t="n">
         <v>5</v>
@@ -1378,7 +1378,7 @@
         <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>16.8</v>
       </c>
       <c r="Q10" t="n">
         <v>50</v>
@@ -1387,13 +1387,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3</v>
+        <v>0.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
         <v>0.5</v>
@@ -1402,7 +1402,7 @@
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.281</v>
+        <v>0.575</v>
       </c>
       <c r="Y10" t="n">
         <v>0.8</v>
@@ -1421,51 +1421,51 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>港股</t>
+          <t>美股</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TENCENT</t>
+          <t>Procter &amp; Gamble Company (The)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>internet content &amp; information</t>
+          <t>household &amp; personal products</t>
         </is>
       </c>
       <c r="E11" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="G11" t="n">
+        <v>64.33</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>2.88</v>
       </c>
-      <c r="F11" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="G11" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.25</v>
-      </c>
       <c r="N11" t="n">
         <v>5</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
         <v>50</v>
@@ -1482,22 +1482,22 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="U11" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0.431</v>
+        <v>0.522</v>
       </c>
       <c r="Y11" t="n">
         <v>0.8</v>
@@ -1521,45 +1521,45 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0883.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CNOOC</t>
+          <t>CCB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>oil &amp; gas e&amp;p</t>
+          <t>banks - diversified</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.14</v>
+        <v>0.62</v>
       </c>
       <c r="F12" t="n">
-        <v>0.168</v>
+        <v>0.094</v>
       </c>
       <c r="G12" t="n">
-        <v>40.02</v>
+        <v>29.98</v>
       </c>
       <c r="H12" t="n">
-        <v>3.52</v>
+        <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.85</v>
+        <v>1.43</v>
       </c>
       <c r="J12" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.26</v>
+        <v>99</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>6.23</v>
+        <v>4.51</v>
       </c>
       <c r="N12" t="n">
         <v>5</v>
@@ -1568,7 +1568,7 @@
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>25.6</v>
+        <v>7.9</v>
       </c>
       <c r="Q12" t="n">
         <v>50</v>
@@ -1577,34 +1577,34 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0.267</v>
+        <v>0.367</v>
       </c>
       <c r="Y12" t="n">
         <v>0.8</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>✅入选</t>
+          <t>❌不入选</t>
         </is>
       </c>
     </row>
@@ -1711,45 +1711,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>0883.HK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CCB</t>
+          <t>CNOOC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>banks - diversified</t>
+          <t>oil &amp; gas e&amp;p</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.62</v>
+        <v>1.14</v>
       </c>
       <c r="F14" t="n">
-        <v>0.094</v>
+        <v>0.168</v>
       </c>
       <c r="G14" t="n">
-        <v>29.98</v>
+        <v>40.02</v>
       </c>
       <c r="H14" t="n">
-        <v>0.89</v>
+        <v>3.52</v>
       </c>
       <c r="I14" t="n">
-        <v>1.43</v>
+        <v>-4.85</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="K14" t="n">
-        <v>99</v>
+        <v>0.26</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.51</v>
+        <v>6.23</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
@@ -1758,7 +1758,7 @@
         <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>7.9</v>
+        <v>25.6</v>
       </c>
       <c r="Q14" t="n">
         <v>50</v>
@@ -1767,34 +1767,34 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>0.367</v>
+        <v>0.267</v>
       </c>
       <c r="Y14" t="n">
         <v>0.8</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>❌不入选</t>
+          <t>✅入选</t>
         </is>
       </c>
     </row>
